--- a/artfynd/A 7575-2024 artfynd.xlsx
+++ b/artfynd/A 7575-2024 artfynd.xlsx
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117455583</v>
+        <v>117455563</v>
       </c>
       <c r="B3" t="n">
         <v>57287</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>487139</v>
+        <v>487110</v>
       </c>
       <c r="R3" t="n">
-        <v>7086111</v>
+        <v>7085873</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117455563</v>
+        <v>117455583</v>
       </c>
       <c r="B4" t="n">
         <v>57287</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>487110</v>
+        <v>487139</v>
       </c>
       <c r="R4" t="n">
-        <v>7085873</v>
+        <v>7086111</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 7575-2024 artfynd.xlsx
+++ b/artfynd/A 7575-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>117455601</v>
       </c>
       <c r="B2" t="n">
-        <v>97753</v>
+        <v>97755</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117455563</v>
+        <v>117455583</v>
       </c>
       <c r="B3" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>487110</v>
+        <v>487139</v>
       </c>
       <c r="R3" t="n">
-        <v>7085873</v>
+        <v>7086111</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117455583</v>
+        <v>117455563</v>
       </c>
       <c r="B4" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>487139</v>
+        <v>487110</v>
       </c>
       <c r="R4" t="n">
-        <v>7086111</v>
+        <v>7085873</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 7575-2024 artfynd.xlsx
+++ b/artfynd/A 7575-2024 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117455601</v>
+        <v>117455563</v>
       </c>
       <c r="B2" t="n">
-        <v>97755</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>487360</v>
+        <v>487110</v>
       </c>
       <c r="R2" t="n">
-        <v>7086143</v>
+        <v>7085873</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117455563</v>
+        <v>117455583</v>
       </c>
       <c r="B3" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>487110</v>
+        <v>487139</v>
       </c>
       <c r="R3" t="n">
-        <v>7085873</v>
+        <v>7086111</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +852,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,37 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117455583</v>
+        <v>117455601</v>
       </c>
       <c r="B4" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>487139</v>
+        <v>487360</v>
       </c>
       <c r="R4" t="n">
-        <v>7086111</v>
+        <v>7086143</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,11 +950,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-05-31</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 7575-2024 artfynd.xlsx
+++ b/artfynd/A 7575-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117455563</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117455583</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,8 +988,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117455601</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>